--- a/src/data/categories.xlsx
+++ b/src/data/categories.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gala\Documents\code\jk3\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gala\Documents\code\jk3\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE2CCC47-3493-4026-81C4-909A0FF6B814}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4167A7A-7D06-4A27-9A00-46058A4A1927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="336" yWindow="396" windowWidth="11808" windowHeight="11076" xr2:uid="{6540F3E8-6E2B-46EF-8B33-43A96A14636B}"/>
+    <workbookView xWindow="276" yWindow="624" windowWidth="11808" windowHeight="11076" xr2:uid="{6540F3E8-6E2B-46EF-8B33-43A96A14636B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,49 +39,436 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="141">
   <si>
     <t>Category Name</t>
   </si>
   <si>
-    <t xml:space="preserve"> Slug</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Parent Category</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Image</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Featured</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Sort Order</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SEO Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Meta Description</t>
-  </si>
-  <si>
-    <t>Electronics</t>
-  </si>
-  <si>
-    <t>electronics</t>
-  </si>
-  <si>
-    <t>Buy Electronics Online - Best Gadgets</t>
-  </si>
-  <si>
-    <t>Discover high-quality electronics, gadgets, and home tech items at affordable prices.</t>
+    <t>Slug</t>
+  </si>
+  <si>
+    <t>Parent Category</t>
+  </si>
+  <si>
+    <t>Image</t>
+  </si>
+  <si>
+    <t>Featured</t>
+  </si>
+  <si>
+    <t>Sort Order</t>
+  </si>
+  <si>
+    <t>SEO Title</t>
+  </si>
+  <si>
+    <t>Meta Description</t>
+  </si>
+  <si>
+    <t>Power Tools</t>
+  </si>
+  <si>
+    <t>power-tools</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Power Tools Online India | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Shop power tools including drills, grinders, saws, rotary hammers and professional equipment at Haryana.Tools.</t>
+  </si>
+  <si>
+    <t>Hand Tools</t>
+  </si>
+  <si>
+    <t>hand-tools</t>
+  </si>
+  <si>
+    <t>Hand Tools Online | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Buy hand tools including pliers, screwdrivers, spanners, hammers and tool kits online.</t>
+  </si>
+  <si>
+    <t>Solar Products</t>
+  </si>
+  <si>
+    <t>solar-products</t>
+  </si>
+  <si>
+    <t>Solar Products Online | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Explore solar panels, inverters, batteries, solar accessories and renewable energy solutions.</t>
+  </si>
+  <si>
+    <t>Industrial Tools</t>
+  </si>
+  <si>
+    <t>industrial-tools</t>
+  </si>
+  <si>
+    <t>Industrial Tools &amp; Equipment | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Browse industrial tools, workshop equipment and heavy-duty machinery online.</t>
+  </si>
+  <si>
+    <t>Welding Equipment</t>
+  </si>
+  <si>
+    <t>welding-equipment</t>
+  </si>
+  <si>
+    <t>Welding Machines &amp; Equipment | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Shop welding machines, electrodes, helmets and welding accessories online.</t>
+  </si>
+  <si>
+    <t>Automotive Tools</t>
+  </si>
+  <si>
+    <t>automotive-tools</t>
+  </si>
+  <si>
+    <t>Automotive Tools Online | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Discover automotive repair tools, garage equipment and vehicle maintenance products.</t>
+  </si>
+  <si>
+    <t>Car Care</t>
+  </si>
+  <si>
+    <t>car-care</t>
+  </si>
+  <si>
+    <t>Car Care Products Online | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Buy car cleaning, detailing and maintenance products for professional and personal use.</t>
+  </si>
+  <si>
+    <t>Safety Equipment</t>
+  </si>
+  <si>
+    <t>safety-equipment</t>
+  </si>
+  <si>
+    <t>Safety Equipment Online | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Browse PPE, helmets, gloves, goggles, safety shoes and workplace safety equipment.</t>
+  </si>
+  <si>
+    <t>Measuring Tools</t>
+  </si>
+  <si>
+    <t>measuring-tools</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Measuring Tools Online | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Shop measuring tapes, laser levels, spirit levels and precision measuring instruments.</t>
+  </si>
+  <si>
+    <t>Abrasives</t>
+  </si>
+  <si>
+    <t>abrasives</t>
+  </si>
+  <si>
+    <t>Abrasives &amp; Grinding Accessories | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Explore cutting discs, grinding wheels, flap discs and abrasive accessories.</t>
+  </si>
+  <si>
+    <t>Cutting Tools</t>
+  </si>
+  <si>
+    <t>cutting-tools</t>
+  </si>
+  <si>
+    <t>Cutting Tools Online | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Buy cutting tools, blades, cutters, hole saws and industrial cutting accessories.</t>
+  </si>
+  <si>
+    <t>Tool Accessories</t>
+  </si>
+  <si>
+    <t>tool-accessories</t>
+  </si>
+  <si>
+    <t>Tool Accessories Online | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Shop drill bits, grinding wheels, batteries, chargers and power tool accessories.</t>
+  </si>
+  <si>
+    <t>Fasteners</t>
+  </si>
+  <si>
+    <t>fasteners</t>
+  </si>
+  <si>
+    <t>Fasteners Online | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Browse nuts, bolts, screws, washers, anchors and fastening solutions.</t>
+  </si>
+  <si>
+    <t>Air Tools</t>
+  </si>
+  <si>
+    <t>air-tools</t>
+  </si>
+  <si>
+    <t>Pneumatic &amp; Air Tools | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Explore air compressors, pneumatic tools and workshop air equipment.</t>
+  </si>
+  <si>
+    <t>Water Pumps</t>
+  </si>
+  <si>
+    <t>water-pumps</t>
+  </si>
+  <si>
+    <t>Water Pumps Online | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Buy domestic, agricultural and industrial water pumps online.</t>
+  </si>
+  <si>
+    <t>Generators</t>
+  </si>
+  <si>
+    <t>generators</t>
+  </si>
+  <si>
+    <t>Portable Generators Online | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Browse portable generators and backup power solutions for home and industry.</t>
+  </si>
+  <si>
+    <t>UPS &amp; Inverters</t>
+  </si>
+  <si>
+    <t>ups-inverters</t>
+  </si>
+  <si>
+    <t>UPS &amp; Inverters Online | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Shop UPS systems, inverters and power backup products online.</t>
+  </si>
+  <si>
+    <t>Batteries</t>
+  </si>
+  <si>
+    <t>batteries</t>
+  </si>
+  <si>
+    <t>Batteries Online | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Buy inverter batteries, solar batteries and backup power batteries.</t>
+  </si>
+  <si>
+    <t>Electrical Supplies</t>
+  </si>
+  <si>
+    <t>electrical-supplies</t>
+  </si>
+  <si>
+    <t>Electrical Supplies Online | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Explore electrical accessories, cables, switches and installation products.</t>
+  </si>
+  <si>
+    <t>Cleaning Equipment</t>
+  </si>
+  <si>
+    <t>cleaning-equipment</t>
+  </si>
+  <si>
+    <t>Cleaning Equipment Online | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Shop pressure washers, vacuum cleaners and industrial cleaning equipment.</t>
+  </si>
+  <si>
+    <t>Garden Tools</t>
+  </si>
+  <si>
+    <t>garden-tools</t>
+  </si>
+  <si>
+    <t>Garden Tools Online | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Buy lawn and garden tools, trimmers, pruners and maintenance equipment.</t>
+  </si>
+  <si>
+    <t>Hardware</t>
+  </si>
+  <si>
+    <t>hardware</t>
+  </si>
+  <si>
+    <t>Hardware Products Online | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Browse hardware products, fittings, locks, hinges and workshop essentials.</t>
+  </si>
+  <si>
+    <t>Ladders &amp; Material Handling</t>
+  </si>
+  <si>
+    <t>ladders-material-handling</t>
+  </si>
+  <si>
+    <t>Ladders &amp; Material Handling Equipment | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Shop ladders, trolleys, pallet trucks and material handling equipment.</t>
+  </si>
+  <si>
+    <t>Income Tax Services</t>
+  </si>
+  <si>
+    <t>income-tax-services</t>
+  </si>
+  <si>
+    <t>Online Income Tax Filing Assistance | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Get online Income Tax Return filing assistance for salaried employees, businesses, freelancers and pensioners across India.</t>
+  </si>
+  <si>
+    <t>GST Services</t>
+  </si>
+  <si>
+    <t>gst-services</t>
+  </si>
+  <si>
+    <t>GST Registration &amp; Return Assistance | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Get assistance with GST registration, GST return filing and GST compliance services.</t>
+  </si>
+  <si>
+    <t>Tools</t>
+  </si>
+  <si>
+    <t>Products</t>
+  </si>
+  <si>
+    <t>Accessories</t>
+  </si>
+  <si>
+    <t>Services</t>
+  </si>
+  <si>
+    <t>Solar</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1645651964715-d200ce0939cc?q=80&amp;w=1170&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1617048530929-0edab8608369?q=80&amp;w=1173&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1668097613572-40b7c11c8727?q=80&amp;w=1170&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
+  </si>
+  <si>
+    <t>https://plus.unsplash.com/premium_photo-1723478480754-436a04e21412?q=80&amp;w=1059&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1508465818649-14a170138405?q=80&amp;w=979&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1530046339160-ce3e530c7d2f?q=80&amp;w=1170&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1520340356584-f9917d1eea6f?q=80&amp;w=1031&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
+  </si>
+  <si>
+    <t>Automotive</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1674558346964-e7196a409880?q=80&amp;w=1170&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1559647746-9b2f216d2dc3?q=80&amp;w=1074&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1564182872950-978e194a05cd?q=80&amp;w=764&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1738162837672-de9d735a9b90?q=80&amp;w=1032&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1776947242128-cade9ec29ab0?q=80&amp;w=1032&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1763888450676-f0f7a3987917?q=80&amp;w=880&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1566527379347-e5e3c8d905e1?q=80&amp;w=1182&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1698031610511-c7a35d121b17?q=80&amp;w=1170&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1650785652040-5a2fc88ce902?q=80&amp;w=1170&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1681263810102-ee12f623a5f3?q=80&amp;w=1032&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1707498633827-936bb448b513?q=80&amp;w=1150&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1553873002-785d775854c9?q=80&amp;w=1170&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1563453392212-326f5e854473?q=80&amp;w=1170&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1621460248083-6271cc4437a8?q=80&amp;w=687&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1550745165-9bc0b252726f?q=80&amp;w=1170&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1584986152939-01133e0d31a2?q=80&amp;w=1074&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1598432439250-0330f9130e14?q=80&amp;w=1170&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1586486855514-8c633cc6fd38?q=80&amp;w=1169&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -90,9 +477,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial Unicode MS"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -452,53 +842,693 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A8F2F70-D1BF-44E2-90B8-B0E4DAB2F558}">
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:H26"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="46.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="101.109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" t="b">
-        <v>1</v>
+      <c r="C2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4">
+        <v>3</v>
+      </c>
+      <c r="G4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D6" t="s">
+        <v>119</v>
+      </c>
+      <c r="E6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6">
+        <v>5</v>
+      </c>
+      <c r="G6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D7" t="s">
+        <v>120</v>
+      </c>
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7">
+        <v>6</v>
+      </c>
+      <c r="G7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" t="s">
+        <v>122</v>
+      </c>
+      <c r="D8" t="s">
+        <v>121</v>
+      </c>
+      <c r="E8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8">
+        <v>7</v>
+      </c>
+      <c r="G8" t="s">
+        <v>35</v>
+      </c>
+      <c r="H8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" t="s">
+        <v>110</v>
+      </c>
+      <c r="D9" t="s">
+        <v>123</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9">
+        <v>8</v>
+      </c>
+      <c r="G9" t="s">
+        <v>39</v>
+      </c>
+      <c r="H9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" t="s">
+        <v>110</v>
+      </c>
+      <c r="D10" t="s">
+        <v>124</v>
+      </c>
+      <c r="E10" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10">
+        <v>9</v>
+      </c>
+      <c r="G10" t="s">
+        <v>44</v>
+      </c>
+      <c r="H10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" t="s">
+        <v>110</v>
+      </c>
+      <c r="D11" t="s">
+        <v>125</v>
+      </c>
+      <c r="E11" t="s">
+        <v>43</v>
+      </c>
+      <c r="F11">
+        <v>10</v>
+      </c>
+      <c r="G11" t="s">
+        <v>48</v>
+      </c>
+      <c r="H11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" t="s">
+        <v>110</v>
+      </c>
+      <c r="D12" t="s">
+        <v>126</v>
+      </c>
+      <c r="E12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12">
         <v>11</v>
+      </c>
+      <c r="G12" t="s">
+        <v>52</v>
+      </c>
+      <c r="H12" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>54</v>
+      </c>
+      <c r="B13" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" t="s">
+        <v>110</v>
+      </c>
+      <c r="D13" t="s">
+        <v>127</v>
+      </c>
+      <c r="E13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13">
+        <v>12</v>
+      </c>
+      <c r="G13" t="s">
+        <v>56</v>
+      </c>
+      <c r="H13" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>58</v>
+      </c>
+      <c r="B14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" t="s">
+        <v>112</v>
+      </c>
+      <c r="D14" t="s">
+        <v>128</v>
+      </c>
+      <c r="E14" t="s">
+        <v>43</v>
+      </c>
+      <c r="F14">
+        <v>13</v>
+      </c>
+      <c r="G14" t="s">
+        <v>60</v>
+      </c>
+      <c r="H14" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>62</v>
+      </c>
+      <c r="B15" t="s">
+        <v>63</v>
+      </c>
+      <c r="C15" t="s">
+        <v>110</v>
+      </c>
+      <c r="D15" t="s">
+        <v>129</v>
+      </c>
+      <c r="E15" t="s">
+        <v>43</v>
+      </c>
+      <c r="F15">
+        <v>14</v>
+      </c>
+      <c r="G15" t="s">
+        <v>64</v>
+      </c>
+      <c r="H15" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>66</v>
+      </c>
+      <c r="B16" t="s">
+        <v>67</v>
+      </c>
+      <c r="C16" t="s">
+        <v>111</v>
+      </c>
+      <c r="D16" t="s">
+        <v>130</v>
+      </c>
+      <c r="E16" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16">
+        <v>15</v>
+      </c>
+      <c r="G16" t="s">
+        <v>68</v>
+      </c>
+      <c r="H16" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>70</v>
+      </c>
+      <c r="B17" t="s">
+        <v>71</v>
+      </c>
+      <c r="C17" t="s">
+        <v>111</v>
+      </c>
+      <c r="D17" t="s">
+        <v>133</v>
+      </c>
+      <c r="E17" t="s">
+        <v>43</v>
+      </c>
+      <c r="F17">
+        <v>16</v>
+      </c>
+      <c r="G17" t="s">
+        <v>72</v>
+      </c>
+      <c r="H17" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>74</v>
+      </c>
+      <c r="B18" t="s">
+        <v>75</v>
+      </c>
+      <c r="C18" t="s">
+        <v>114</v>
+      </c>
+      <c r="D18" t="s">
+        <v>131</v>
+      </c>
+      <c r="E18" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18">
+        <v>17</v>
+      </c>
+      <c r="G18" t="s">
+        <v>76</v>
+      </c>
+      <c r="H18" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>78</v>
+      </c>
+      <c r="B19" t="s">
+        <v>79</v>
+      </c>
+      <c r="C19" t="s">
+        <v>114</v>
+      </c>
+      <c r="D19" t="s">
+        <v>132</v>
+      </c>
+      <c r="E19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19">
+        <v>18</v>
+      </c>
+      <c r="G19" t="s">
+        <v>80</v>
+      </c>
+      <c r="H19" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>82</v>
+      </c>
+      <c r="B20" t="s">
+        <v>83</v>
+      </c>
+      <c r="C20" t="s">
+        <v>112</v>
+      </c>
+      <c r="D20" t="s">
+        <v>134</v>
+      </c>
+      <c r="E20" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20">
+        <v>19</v>
+      </c>
+      <c r="G20" t="s">
+        <v>84</v>
+      </c>
+      <c r="H20" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>86</v>
+      </c>
+      <c r="B21" t="s">
+        <v>87</v>
+      </c>
+      <c r="C21" t="s">
+        <v>110</v>
+      </c>
+      <c r="D21" t="s">
+        <v>135</v>
+      </c>
+      <c r="E21" t="s">
+        <v>43</v>
+      </c>
+      <c r="F21">
+        <v>20</v>
+      </c>
+      <c r="G21" t="s">
+        <v>88</v>
+      </c>
+      <c r="H21" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>90</v>
+      </c>
+      <c r="B22" t="s">
+        <v>91</v>
+      </c>
+      <c r="C22" t="s">
+        <v>110</v>
+      </c>
+      <c r="D22" t="s">
+        <v>136</v>
+      </c>
+      <c r="E22" t="s">
+        <v>43</v>
+      </c>
+      <c r="F22">
+        <v>21</v>
+      </c>
+      <c r="G22" t="s">
+        <v>92</v>
+      </c>
+      <c r="H22" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>94</v>
+      </c>
+      <c r="B23" t="s">
+        <v>95</v>
+      </c>
+      <c r="C23" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23" t="s">
+        <v>137</v>
+      </c>
+      <c r="E23" t="s">
+        <v>43</v>
+      </c>
+      <c r="F23">
+        <v>22</v>
+      </c>
+      <c r="G23" t="s">
+        <v>96</v>
+      </c>
+      <c r="H23" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>98</v>
+      </c>
+      <c r="B24" t="s">
+        <v>99</v>
+      </c>
+      <c r="C24" t="s">
+        <v>110</v>
+      </c>
+      <c r="D24" t="s">
+        <v>138</v>
+      </c>
+      <c r="E24" t="s">
+        <v>43</v>
+      </c>
+      <c r="F24">
+        <v>23</v>
+      </c>
+      <c r="G24" t="s">
+        <v>100</v>
+      </c>
+      <c r="H24" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>102</v>
+      </c>
+      <c r="B25" t="s">
+        <v>103</v>
+      </c>
+      <c r="C25" t="s">
+        <v>113</v>
+      </c>
+      <c r="D25" t="s">
+        <v>139</v>
+      </c>
+      <c r="E25" t="s">
+        <v>10</v>
+      </c>
+      <c r="F25">
+        <v>24</v>
+      </c>
+      <c r="G25" t="s">
+        <v>104</v>
+      </c>
+      <c r="H25" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>106</v>
+      </c>
+      <c r="B26" t="s">
+        <v>107</v>
+      </c>
+      <c r="C26" t="s">
+        <v>113</v>
+      </c>
+      <c r="D26" t="s">
+        <v>140</v>
+      </c>
+      <c r="E26" t="s">
+        <v>10</v>
+      </c>
+      <c r="F26">
+        <v>25</v>
+      </c>
+      <c r="G26" t="s">
+        <v>108</v>
+      </c>
+      <c r="H26" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/src/data/categories.xlsx
+++ b/src/data/categories.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gala\Documents\code\jk3\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4167A7A-7D06-4A27-9A00-46058A4A1927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27A0B06E-FF6B-4867-8CAC-D9A98F638A4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="276" yWindow="624" windowWidth="11808" windowHeight="11076" xr2:uid="{6540F3E8-6E2B-46EF-8B33-43A96A14636B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6540F3E8-6E2B-46EF-8B33-43A96A14636B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="142">
   <si>
     <t>Category Name</t>
   </si>
@@ -462,6 +462,9 @@
   </si>
   <si>
     <t>https://images.unsplash.com/photo-1586486855514-8c633cc6fd38?q=80&amp;w=1169&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
+  </si>
+  <si>
+    <t>Accounting Services</t>
   </si>
 </sst>
 </file>
@@ -842,7 +845,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A8F2F70-D1BF-44E2-90B8-B0E4DAB2F558}">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.6640625" bestFit="1" customWidth="1"/>
@@ -1531,6 +1534,11 @@
         <v>109</v>
       </c>
     </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>141</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/data/categories.xlsx
+++ b/src/data/categories.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gala\Documents\code\jk3\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37F17B02-A8B9-4792-B672-646588555355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFB97AAD-1620-4339-A29F-57AF0DD6C54A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6540F3E8-6E2B-46EF-8B33-43A96A14636B}"/>
   </bookViews>
@@ -104,24 +104,15 @@
     <t>Services</t>
   </si>
   <si>
-    <t>https://images.unsplash.com/photo-1598432439250-0330f9130e14?q=80&amp;w=1170&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
-  </si>
-  <si>
     <t>(None)</t>
   </si>
   <si>
-    <t>https://images.unsplash.com/photo-1504148455328-c376907d081c</t>
-  </si>
-  <si>
     <t>Power Tools Online | Haryana.Tools</t>
   </si>
   <si>
     <t>Explore heavy-duty power tools, cordless drills, angle grinders, and professional equipment at Haryana.Tools.</t>
   </si>
   <si>
-    <t>https://images.unsplash.com/photo-1530124566582-a618bc2615dc</t>
-  </si>
-  <si>
     <t>Shop professional hand tools, spanners, pliers, screwdrivers, and workshop tool kits.</t>
   </si>
   <si>
@@ -131,9 +122,6 @@
     <t>car-care-products</t>
   </si>
   <si>
-    <t>https://images.unsplash.com/photo-1619642751034-765dfdf7c58e</t>
-  </si>
-  <si>
     <t>Discover premium car care products, waxes, polishes, ceramic coatings, and detailing accessories.</t>
   </si>
   <si>
@@ -143,9 +131,6 @@
     <t>solar-panels-systems</t>
   </si>
   <si>
-    <t>https://images.unsplash.com/photo-1509391365360-e835f377e169</t>
-  </si>
-  <si>
     <t>Solar Panels &amp; Systems | Haryana.Tools</t>
   </si>
   <si>
@@ -158,9 +143,6 @@
     <t>cordless-tools</t>
   </si>
   <si>
-    <t>https://images.unsplash.com/photo-1572981779307-38b8cabb2407</t>
-  </si>
-  <si>
     <t>Cordless Power Tools | Haryana.Tools</t>
   </si>
   <si>
@@ -173,9 +155,6 @@
     <t>cutting-abrasive-tools</t>
   </si>
   <si>
-    <t>https://images.unsplash.com/photo-1581092160607-ee22621dd758</t>
-  </si>
-  <si>
     <t>Cutting &amp; Abrasive Tools | Haryana.Tools</t>
   </si>
   <si>
@@ -188,9 +167,6 @@
     <t>workshop-equipment</t>
   </si>
   <si>
-    <t>https://images.unsplash.com/photo-1581092335397-9583fe92d232</t>
-  </si>
-  <si>
     <t>Workshop Equipment &amp; Gear | Haryana.Tools</t>
   </si>
   <si>
@@ -203,13 +179,37 @@
     <t>solar-inverters-batteries</t>
   </si>
   <si>
-    <t>https://images.unsplash.com/photo-1617788138017-80ad40651399</t>
-  </si>
-  <si>
     <t>Solar Inverters &amp; Batteries | Haryana.Tools</t>
   </si>
   <si>
     <t>Discover solar inverters, PCUs, lithium and tubular batteries for power backup.</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/vector-1738926430795-3fe593ff63af?q=80&amp;w=880&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/vector-1777988015390-a1cbdf709026?q=80&amp;w=880&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/vector-1739672910396-94762d7c3be6?q=80&amp;w=880&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/vector-1774825216949-b0cbadb9ca9c?q=80&amp;w=913&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1645651964715-d200ce0939cc?q=80&amp;w=1470&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1773875342538-a45969eb78e5?q=80&amp;w=742&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1683115099413-5b7d85c2950c?q=80&amp;w=1476&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1713544123641-5328f51964e4?q=80&amp;w=1013&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1775363949839-af16004b7815?q=80&amp;w=1470&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
   </si>
 </sst>
 </file>
@@ -653,7 +653,7 @@
     <col min="1" max="1" width="25.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="59.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.33203125" customWidth="1"/>
     <col min="5" max="5" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="42.109375" customWidth="1"/>
@@ -694,10 +694,10 @@
         <v>9</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>10</v>
@@ -706,13 +706,13 @@
         <v>1</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
@@ -720,10 +720,10 @@
         <v>12</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>10</v>
@@ -735,21 +735,21 @@
         <v>13</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>10</v>
@@ -761,21 +761,21 @@
         <v>14</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>10</v>
@@ -784,24 +784,24 @@
         <v>4</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>10</v>
@@ -810,24 +810,24 @@
         <v>5</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>15</v>
@@ -836,24 +836,24 @@
         <v>6</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>15</v>
@@ -862,24 +862,24 @@
         <v>7</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>10</v>
@@ -888,13 +888,13 @@
         <v>8</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>16</v>
       </c>
@@ -905,7 +905,7 @@
         <v>20</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>21</v>
+        <v>56</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>10</v>
@@ -921,16 +921,6 @@
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" display="https://www.google.com/search?q=https://images.unsplash.com/photo-1504148455328-c376907d081c" xr:uid="{5E0E5CAB-D257-47FB-A9B3-AA178284D582}"/>
-    <hyperlink ref="D3" r:id="rId2" display="https://www.google.com/search?q=https://images.unsplash.com/photo-1530124566582-a618bc2615dc" xr:uid="{B0859C9E-E89B-4181-80CC-1CC514769368}"/>
-    <hyperlink ref="D4" r:id="rId3" display="https://www.google.com/search?q=https://images.unsplash.com/photo-1619642751034-765dfdf7c58e" xr:uid="{34C2C6EC-D39F-4CCF-9BBF-AFDE1AE7AE42}"/>
-    <hyperlink ref="D5" r:id="rId4" display="https://www.google.com/search?q=https://images.unsplash.com/photo-1509391365360-e835f377e169" xr:uid="{9339D8F7-62FB-4796-82FC-87E2EB32E4F5}"/>
-    <hyperlink ref="D6" r:id="rId5" display="https://www.google.com/search?q=https://images.unsplash.com/photo-1572981779307-38b8cabb2407" xr:uid="{44FB7213-B0BC-4895-87AC-400BA4D22302}"/>
-    <hyperlink ref="D7" r:id="rId6" display="https://www.google.com/search?q=https://images.unsplash.com/photo-1581092160607-ee22621dd758" xr:uid="{74075612-83C2-44D2-BB1A-9E7B200E7B4F}"/>
-    <hyperlink ref="D8" r:id="rId7" display="https://www.google.com/search?q=https://images.unsplash.com/photo-1581092335397-9583fe92d232" xr:uid="{024E7D56-D98E-4A2B-956E-88A96A76B4E3}"/>
-    <hyperlink ref="D9" r:id="rId8" display="https://www.google.com/search?q=https://images.unsplash.com/photo-1617788138017-80ad40651399" xr:uid="{BB1A1CAB-A5D0-440F-8728-D0FC236E1146}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>